--- a/data/results of data sharing requests.xlsx
+++ b/data/results of data sharing requests.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Ian/git/repository-of-published-irap-data/data/requests for data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Ian/git/repository-of-published-irap-data/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45F6E106-266E-8843-8435-34E8DC19A903}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CA4D958-A2CE-F849-8C12-D45EF6BC0B22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="18380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="32780" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="contacted" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="349">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="345">
   <si>
     <t>72LX2MUL</t>
   </si>
@@ -822,9 +822,6 @@
   </si>
   <si>
     <t>bast, Alasiri, Kolts</t>
-  </si>
-  <si>
-    <t>note: no email for corrisponding author (kavanagh) could be obtained. Dbh couldn't supply one.</t>
   </si>
   <si>
     <t>murphy; kelly; foody, maloney</t>
@@ -1003,15 +1000,6 @@
     <t>hendricks and dbh said they don’t have data, egger will look into obtaining the data from archives and pointed me to ciara, ciara and yvonne don’t have the data and pointed me to hentriks</t>
   </si>
   <si>
-    <t>note: no email for corrisponding author (kavanagh) could be obtained. Dbh couldn't supply one. YBH said she doesn't have the data</t>
-  </si>
-  <si>
-    <t>note: no email for corrisponding author (kavanagh) could be obtained. Dbh couldn't supply one. YBH and mcenteggart said they don't have the data.</t>
-  </si>
-  <si>
-    <t>note: no email for corrisponding author (kavanagh) could be obtained. Dbh couldn't supply one.YBH and mcenteggart said they don't have the data.</t>
-  </si>
-  <si>
     <t>barnes-holmes, d; leech</t>
   </si>
   <si>
@@ -1083,9 +1071,6 @@
   </si>
   <si>
     <t>"Let me prepare some data to share." on 15-03-2023. Reminder email with deadline sent a month before deadline.</t>
-  </si>
-  <si>
-    <t>declined saying that the data exists and they'd like to share but ethics prevent it.</t>
   </si>
   <si>
     <t xml:space="preserve">SHARED DATA BUT CANNOT BE MADE PUBLIC PER THE AUTHORS' ETHICAL REQUIREMENTS. </t>
@@ -1111,12 +1096,6 @@
     </r>
   </si>
   <si>
-    <t>finn didn't reply, dbh, ybh and mcenteggart said they doesn't have the data. Finn asked a mutual colleague if I received the data from him (implying he sent it), and so I emailed him again and provided an alternative email address for him to reply to, but I haven't received any direct reply from him.</t>
-  </si>
-  <si>
-    <t>finn didn't reply, dbh, ybh and mcenteggart said they doesn't have the data. Finn asked a mutual colleague if I received the data from him (implying he sent it), and so I emailed him again and provided an alternative email address for him to reply to, but</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="12"/>
@@ -1167,6 +1146,15 @@
       </rPr>
       <t>NB data was shared but not by person specified in DAS.</t>
     </r>
+  </si>
+  <si>
+    <t xml:space="preserve">DBH and YBH said they don't have the data. Email for Deirdre eventually tracked down through another colleague. Said she will liase with Ugent about what data she can share. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">finn didn't reply, dbh, ybh and mcenteggart said they doesn't have the data. Finn asked a mutual colleague if I received the data from him (implying he sent it), and so I emailed him again and provided an alternative email address for him to reply to, but I haven't received any direct reply from him. Jan Lammartyn at UGent said he will contact me with a data sharing agreement for Finn's data, but no specific details of which studies or a timeline were offered. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">declined saying that the data exists and they'd like to share but ethics prevent it. Jan Lammartyn at UGent said he will contact me with a data sharing agreement for Finn's data, but no specific details of which studies or a timeline were offered. </t>
   </si>
 </sst>
 </file>
@@ -1325,7 +1313,7 @@
       <name val="Calibri (Body)"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1503,12 +1491,6 @@
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -1690,17 +1672,17 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -2102,34 +2084,34 @@
         <v>228</v>
       </c>
       <c r="I1" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="J1" s="3" t="s">
         <v>270</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="M1" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="N1" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="O1" s="4" t="s">
         <v>275</v>
       </c>
-      <c r="N1" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="O1" s="4" t="s">
-        <v>276</v>
-      </c>
       <c r="P1" s="4" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="Q1" s="3" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="R1" s="3" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="68" x14ac:dyDescent="0.2">
@@ -2162,7 +2144,7 @@
         <v>248</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="K2" s="5">
         <v>44995</v>
@@ -2177,16 +2159,16 @@
         <v>1</v>
       </c>
       <c r="O2" s="4" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="P2" s="4" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="Q2" s="3" t="b">
         <v>0</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="3" spans="1:18" ht="102" x14ac:dyDescent="0.2">
@@ -2219,7 +2201,7 @@
         <v>255</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="K3" s="5">
         <v>45008</v>
@@ -2230,20 +2212,20 @@
       <c r="M3" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="N3" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="O3" s="8" t="s">
-        <v>344</v>
+      <c r="N3" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="O3" s="10" t="s">
+        <v>337</v>
       </c>
       <c r="P3" s="4" t="s">
-        <v>307</v>
-      </c>
-      <c r="Q3" s="7" t="b">
+        <v>306</v>
+      </c>
+      <c r="Q3" s="9" t="b">
         <v>0</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="4" spans="1:18" ht="34" x14ac:dyDescent="0.2">
@@ -2276,7 +2258,7 @@
         <v>255</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="K4" s="5">
         <v>45006</v>
@@ -2294,13 +2276,13 @@
         <v>253</v>
       </c>
       <c r="P4" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="Q4" s="3" t="b">
         <v>0</v>
       </c>
       <c r="R4" s="3" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="5" spans="1:18" ht="68" x14ac:dyDescent="0.2">
@@ -2348,7 +2330,7 @@
         <v>1</v>
       </c>
       <c r="O5" s="4" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="P5" s="4" t="b">
         <v>0</v>
@@ -2462,16 +2444,16 @@
         <v>0</v>
       </c>
       <c r="O7" s="4" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="P7" s="4" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="Q7" s="3" t="b">
         <v>0</v>
       </c>
       <c r="R7" s="3" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="8" spans="1:18" ht="51" x14ac:dyDescent="0.2">
@@ -2504,7 +2486,7 @@
         <v>247</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="K8" s="5">
         <v>44995</v>
@@ -2519,16 +2501,16 @@
         <v>1</v>
       </c>
       <c r="O8" s="4" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="P8" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="Q8" s="3" t="b">
         <v>1</v>
       </c>
       <c r="R8" s="3" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="9" spans="1:18" ht="34" x14ac:dyDescent="0.2">
@@ -2618,7 +2600,7 @@
         <v>247</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="K10" s="5">
         <v>45008</v>
@@ -2693,13 +2675,13 @@
         <v>252</v>
       </c>
       <c r="P11" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="Q11" s="3" t="b">
         <v>0</v>
       </c>
       <c r="R11" s="3" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="12" spans="1:18" ht="68" x14ac:dyDescent="0.2">
@@ -2732,7 +2714,7 @@
         <v>246</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="K12" s="5">
         <v>45013</v>
@@ -2747,16 +2729,16 @@
         <v>1</v>
       </c>
       <c r="O12" s="4" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="P12" s="4" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="Q12" s="3" t="b">
         <v>1</v>
       </c>
       <c r="R12" s="3" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="51" x14ac:dyDescent="0.2">
@@ -2789,7 +2771,7 @@
         <v>246</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="K13" s="5">
         <v>45013</v>
@@ -2804,7 +2786,7 @@
         <v>1</v>
       </c>
       <c r="O13" s="4" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="P13" s="4" t="b">
         <v>0</v>
@@ -2851,7 +2833,7 @@
       <c r="K14" s="5">
         <v>44995</v>
       </c>
-      <c r="L14" s="10" t="b">
+      <c r="L14" s="8" t="b">
         <v>0</v>
       </c>
       <c r="M14" s="3" t="b">
@@ -2860,8 +2842,8 @@
       <c r="N14" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="O14" s="9" t="s">
-        <v>330</v>
+      <c r="O14" s="7" t="s">
+        <v>326</v>
       </c>
       <c r="P14" s="4" t="b">
         <v>0</v>
@@ -2918,7 +2900,7 @@
         <v>0</v>
       </c>
       <c r="O15" s="4" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="P15" s="4" t="b">
         <v>0</v>
@@ -2960,7 +2942,7 @@
         <v>249</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="K16" s="5">
         <v>44995</v>
@@ -2975,7 +2957,7 @@
         <v>0</v>
       </c>
       <c r="O16" s="4" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="P16" s="4" t="b">
         <v>0</v>
@@ -2987,7 +2969,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="17" spans="1:19" ht="102" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:19" ht="153" x14ac:dyDescent="0.2">
       <c r="A17" s="3">
         <v>16</v>
       </c>
@@ -3017,7 +2999,7 @@
         <v>247</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="K17" s="5">
         <v>44995</v>
@@ -3025,14 +3007,14 @@
       <c r="L17" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="M17" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="N17" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="O17" s="8" t="s">
-        <v>342</v>
+      <c r="M17" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="N17" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="O17" s="10" t="s">
+        <v>343</v>
       </c>
       <c r="P17" s="4" t="b">
         <v>0</v>
@@ -3045,7 +3027,7 @@
       </c>
       <c r="S17" s="1"/>
     </row>
-    <row r="18" spans="1:19" ht="85" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:19" ht="153" x14ac:dyDescent="0.2">
       <c r="A18" s="3">
         <v>17</v>
       </c>
@@ -3075,7 +3057,7 @@
         <v>247</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="K18" s="5">
         <v>44995</v>
@@ -3083,13 +3065,13 @@
       <c r="L18" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="M18" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="N18" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="O18" s="8" t="s">
+      <c r="M18" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="N18" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="O18" s="10" t="s">
         <v>343</v>
       </c>
       <c r="P18" s="4" t="b">
@@ -3130,10 +3112,10 @@
         <v>208</v>
       </c>
       <c r="I19" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="J19" s="3" t="s">
         <v>282</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>283</v>
       </c>
       <c r="K19" s="5">
         <v>45007</v>
@@ -3148,16 +3130,16 @@
         <v>0</v>
       </c>
       <c r="O19" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="P19" s="4" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="Q19" s="3" t="b">
         <v>0</v>
       </c>
       <c r="R19" s="3" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="S19" s="1"/>
     </row>
@@ -3189,7 +3171,7 @@
         <v>247</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="K20" s="5">
         <v>45005</v>
@@ -3204,7 +3186,7 @@
         <v>0</v>
       </c>
       <c r="O20" s="4" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="P20" s="4" t="b">
         <v>0</v>
@@ -3247,7 +3229,7 @@
         <v>247</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="K21" s="5">
         <v>45005</v>
@@ -3262,7 +3244,7 @@
         <v>0</v>
       </c>
       <c r="O21" s="4" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="P21" s="4" t="b">
         <v>0</v>
@@ -3313,26 +3295,26 @@
       <c r="L22" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="M22" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="N22" s="3" t="b">
+      <c r="M22" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="N22" s="9" t="b">
         <v>0</v>
       </c>
       <c r="O22" s="4" t="s">
-        <v>317</v>
+        <v>342</v>
       </c>
       <c r="P22" s="4" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="Q22" s="3" t="b">
         <v>0</v>
       </c>
       <c r="R22" s="3" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="23" spans="1:19" ht="51" x14ac:dyDescent="0.2">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" ht="68" x14ac:dyDescent="0.2">
       <c r="A23" s="3">
         <v>22</v>
       </c>
@@ -3362,7 +3344,7 @@
         <v>249</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="K23" s="5">
         <v>44995</v>
@@ -3370,14 +3352,14 @@
       <c r="L23" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="M23" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="N23" s="3" t="b">
+      <c r="M23" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="N23" s="9" t="b">
         <v>0</v>
       </c>
       <c r="O23" s="4" t="s">
-        <v>318</v>
+        <v>342</v>
       </c>
       <c r="P23" s="4" t="b">
         <v>0</v>
@@ -3389,7 +3371,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="24" spans="1:19" ht="51" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:19" ht="68" x14ac:dyDescent="0.2">
       <c r="A24" s="3">
         <v>23</v>
       </c>
@@ -3427,14 +3409,14 @@
       <c r="L24" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="M24" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="N24" s="3" t="b">
+      <c r="M24" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="N24" s="9" t="b">
         <v>0</v>
       </c>
       <c r="O24" s="4" t="s">
-        <v>319</v>
+        <v>342</v>
       </c>
       <c r="P24" s="4" t="b">
         <v>0</v>
@@ -3446,7 +3428,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="25" spans="1:19" ht="34" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:19" ht="68" x14ac:dyDescent="0.2">
       <c r="A25" s="3">
         <v>24</v>
       </c>
@@ -3484,14 +3466,14 @@
       <c r="L25" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="M25" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="N25" s="3" t="b">
+      <c r="M25" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="N25" s="9" t="b">
         <v>0</v>
       </c>
       <c r="O25" s="4" t="s">
-        <v>263</v>
+        <v>342</v>
       </c>
       <c r="P25" s="4" t="b">
         <v>0</v>
@@ -3533,7 +3515,7 @@
         <v>247</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="K26" s="5">
         <v>44999</v>
@@ -3548,16 +3530,16 @@
         <v>0</v>
       </c>
       <c r="O26" s="4" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="P26" s="4" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="Q26" s="3" t="b">
         <v>0</v>
       </c>
       <c r="R26" s="3" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="27" spans="1:19" ht="51" x14ac:dyDescent="0.2">
@@ -3590,7 +3572,7 @@
         <v>247</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="K27" s="5">
         <v>44999</v>
@@ -3605,7 +3587,7 @@
         <v>0</v>
       </c>
       <c r="O27" s="4" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="P27" s="4" t="b">
         <v>0</v>
@@ -3647,7 +3629,7 @@
         <v>247</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="K28" s="5">
         <v>44999</v>
@@ -3662,7 +3644,7 @@
         <v>0</v>
       </c>
       <c r="O28" s="4" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="P28" s="4" t="b">
         <v>0</v>
@@ -3704,7 +3686,7 @@
         <v>249</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="K29" s="5">
         <v>44995</v>
@@ -3722,13 +3704,13 @@
         <v>244</v>
       </c>
       <c r="P29" s="4" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="Q29" s="3" t="b">
         <v>0</v>
       </c>
       <c r="R29" s="3" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="30" spans="1:19" ht="34" x14ac:dyDescent="0.2">
@@ -3776,7 +3758,7 @@
         <v>0</v>
       </c>
       <c r="O30" s="4" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="P30" s="4" t="b">
         <v>0</v>
@@ -3829,20 +3811,20 @@
       <c r="M31" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="N31" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="O31" s="8" t="s">
-        <v>337</v>
+      <c r="N31" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="O31" s="10" t="s">
+        <v>333</v>
       </c>
       <c r="P31" s="4" t="s">
-        <v>305</v>
-      </c>
-      <c r="Q31" s="7" t="b">
+        <v>304</v>
+      </c>
+      <c r="Q31" s="9" t="b">
         <v>0</v>
       </c>
       <c r="R31" s="3" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="32" spans="1:19" ht="51" x14ac:dyDescent="0.2">
@@ -3886,20 +3868,20 @@
       <c r="M32" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="N32" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="O32" s="8" t="s">
-        <v>337</v>
+      <c r="N32" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="O32" s="10" t="s">
+        <v>333</v>
       </c>
       <c r="P32" s="4" t="s">
-        <v>291</v>
-      </c>
-      <c r="Q32" s="7" t="b">
+        <v>290</v>
+      </c>
+      <c r="Q32" s="9" t="b">
         <v>0</v>
       </c>
       <c r="R32" s="3" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.2">
@@ -4003,13 +3985,13 @@
       </c>
       <c r="O34" s="4"/>
       <c r="P34" s="4" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="Q34" s="3" t="b">
         <v>1</v>
       </c>
       <c r="R34" s="3" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="35" spans="1:18" ht="51" x14ac:dyDescent="0.2">
@@ -4056,17 +4038,17 @@
       <c r="N35" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="O35" s="9" t="s">
-        <v>296</v>
+      <c r="O35" s="7" t="s">
+        <v>295</v>
       </c>
       <c r="P35" s="4" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="Q35" s="3" t="b">
         <v>1</v>
       </c>
       <c r="R35" s="3" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="36" spans="1:18" ht="17" x14ac:dyDescent="0.2">
@@ -4114,7 +4096,7 @@
         <v>0</v>
       </c>
       <c r="O36" s="4" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="P36" s="4" t="b">
         <v>0</v>
@@ -4171,16 +4153,16 @@
         <v>1</v>
       </c>
       <c r="O37" s="4" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="P37" s="4" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="Q37" s="3" t="b">
         <v>0</v>
       </c>
       <c r="R37" s="3" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="38" spans="1:18" ht="34" x14ac:dyDescent="0.2">
@@ -4227,8 +4209,8 @@
       <c r="N38" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="O38" s="9" t="s">
-        <v>340</v>
+      <c r="O38" s="7" t="s">
+        <v>335</v>
       </c>
       <c r="P38" s="3" t="b">
         <v>1</v>
@@ -4339,8 +4321,8 @@
       <c r="N40" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="O40" s="9" t="s">
-        <v>340</v>
+      <c r="O40" s="7" t="s">
+        <v>335</v>
       </c>
       <c r="P40" s="3" t="b">
         <v>0</v>
@@ -4492,7 +4474,7 @@
         <v>247</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="K43" s="5">
         <v>45013</v>
@@ -4572,7 +4554,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="45" spans="1:18" ht="34" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:18" ht="85" x14ac:dyDescent="0.2">
       <c r="A45" s="3">
         <v>44</v>
       </c>
@@ -4602,7 +4584,7 @@
         <v>247</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="K45" s="5">
         <v>45006</v>
@@ -4610,14 +4592,14 @@
       <c r="L45" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="M45" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="N45" s="3" t="b">
+      <c r="M45" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="N45" s="9" t="b">
         <v>0</v>
       </c>
       <c r="O45" s="4" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="P45" s="4" t="b">
         <v>0</v>
@@ -4659,7 +4641,7 @@
         <v>247</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="K46" s="5">
         <v>45013</v>
@@ -4674,7 +4656,7 @@
         <v>0</v>
       </c>
       <c r="O46" s="4" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="P46" s="4" t="b">
         <v>0</v>
@@ -4787,13 +4769,13 @@
       </c>
       <c r="O48" s="4"/>
       <c r="P48" s="4" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="Q48" s="3" t="b">
         <v>0</v>
       </c>
       <c r="R48" s="3" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="49" spans="1:18" ht="17" x14ac:dyDescent="0.2">
@@ -4841,7 +4823,7 @@
         <v>1</v>
       </c>
       <c r="O49" s="4" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="P49" s="4" t="b">
         <v>0</v>
@@ -4880,10 +4862,10 @@
         <v>219</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="K50" s="5">
         <v>45013</v>
@@ -4894,20 +4876,20 @@
       <c r="M50" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="N50" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="O50" s="8" t="s">
-        <v>345</v>
+      <c r="N50" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="O50" s="10" t="s">
+        <v>338</v>
       </c>
       <c r="P50" s="4" t="s">
-        <v>308</v>
-      </c>
-      <c r="Q50" s="7" t="b">
+        <v>307</v>
+      </c>
+      <c r="Q50" s="9" t="b">
         <v>0</v>
       </c>
       <c r="R50" s="3" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="51" spans="1:18" ht="51" x14ac:dyDescent="0.2">
@@ -4951,20 +4933,20 @@
       <c r="M51" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="N51" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="O51" s="8" t="s">
-        <v>338</v>
+      <c r="N51" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="O51" s="10" t="s">
+        <v>334</v>
       </c>
       <c r="P51" s="4" t="s">
-        <v>290</v>
-      </c>
-      <c r="Q51" s="7" t="b">
+        <v>289</v>
+      </c>
+      <c r="Q51" s="9" t="b">
         <v>0</v>
       </c>
       <c r="R51" s="3" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="52" spans="1:18" ht="51" x14ac:dyDescent="0.2">
@@ -4997,7 +4979,7 @@
         <v>247</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="K52" s="5">
         <v>45013</v>
@@ -5013,13 +4995,13 @@
       </c>
       <c r="O52" s="4"/>
       <c r="P52" s="4" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="Q52" s="3" t="b">
         <v>0</v>
       </c>
       <c r="R52" s="3" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="53" spans="1:18" ht="51" x14ac:dyDescent="0.2">
@@ -5052,7 +5034,7 @@
         <v>247</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="K53" s="5">
         <v>44995</v>
@@ -5068,13 +5050,13 @@
       </c>
       <c r="O53" s="4"/>
       <c r="P53" s="4" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="Q53" s="3" t="b">
         <v>0</v>
       </c>
       <c r="R53" s="3" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
   </sheetData>
@@ -5135,7 +5117,7 @@
         <v>233</v>
       </c>
       <c r="O1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.2">
@@ -5183,7 +5165,7 @@
         <v>233</v>
       </c>
       <c r="O2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.2">
@@ -5231,7 +5213,7 @@
         <v>233</v>
       </c>
       <c r="O3" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
   </sheetData>

--- a/data/results of data sharing requests.xlsx
+++ b/data/results of data sharing requests.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Ian/git/repository-of-published-irap-data/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CA4D958-A2CE-F849-8C12-D45EF6BC0B22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C95689FD-6523-E043-83D2-6DD8BEBC831B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="32780" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1654,7 +1654,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1677,12 +1677,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -2212,16 +2206,16 @@
       <c r="M3" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="N3" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="O3" s="10" t="s">
+      <c r="N3" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="O3" s="4" t="s">
         <v>337</v>
       </c>
       <c r="P3" s="4" t="s">
         <v>306</v>
       </c>
-      <c r="Q3" s="9" t="b">
+      <c r="Q3" s="3" t="b">
         <v>0</v>
       </c>
       <c r="R3" s="3" t="s">
@@ -3007,13 +3001,13 @@
       <c r="L17" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="M17" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="N17" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="O17" s="10" t="s">
+      <c r="M17" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="N17" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="O17" s="4" t="s">
         <v>343</v>
       </c>
       <c r="P17" s="4" t="b">
@@ -3065,13 +3059,13 @@
       <c r="L18" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="M18" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="N18" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="O18" s="10" t="s">
+      <c r="M18" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="N18" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="O18" s="4" t="s">
         <v>343</v>
       </c>
       <c r="P18" s="4" t="b">
@@ -3295,10 +3289,10 @@
       <c r="L22" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="M22" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="N22" s="9" t="b">
+      <c r="M22" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="N22" s="3" t="b">
         <v>0</v>
       </c>
       <c r="O22" s="4" t="s">
@@ -3352,10 +3346,10 @@
       <c r="L23" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="M23" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="N23" s="9" t="b">
+      <c r="M23" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="N23" s="3" t="b">
         <v>0</v>
       </c>
       <c r="O23" s="4" t="s">
@@ -3409,10 +3403,10 @@
       <c r="L24" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="M24" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="N24" s="9" t="b">
+      <c r="M24" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3" t="b">
         <v>0</v>
       </c>
       <c r="O24" s="4" t="s">
@@ -3466,10 +3460,10 @@
       <c r="L25" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="M25" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="N25" s="9" t="b">
+      <c r="M25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="N25" s="3" t="b">
         <v>0</v>
       </c>
       <c r="O25" s="4" t="s">
@@ -3811,16 +3805,16 @@
       <c r="M31" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="N31" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="O31" s="10" t="s">
+      <c r="N31" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="O31" s="4" t="s">
         <v>333</v>
       </c>
       <c r="P31" s="4" t="s">
         <v>304</v>
       </c>
-      <c r="Q31" s="9" t="b">
+      <c r="Q31" s="3" t="b">
         <v>0</v>
       </c>
       <c r="R31" s="3" t="s">
@@ -3868,16 +3862,16 @@
       <c r="M32" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="N32" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="O32" s="10" t="s">
+      <c r="N32" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="O32" s="4" t="s">
         <v>333</v>
       </c>
       <c r="P32" s="4" t="s">
         <v>290</v>
       </c>
-      <c r="Q32" s="9" t="b">
+      <c r="Q32" s="3" t="b">
         <v>0</v>
       </c>
       <c r="R32" s="3" t="s">
@@ -4036,7 +4030,7 @@
         <v>0</v>
       </c>
       <c r="N35" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O35" s="7" t="s">
         <v>295</v>
@@ -4592,10 +4586,10 @@
       <c r="L45" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="M45" s="9" t="b">
-        <v>1</v>
-      </c>
-      <c r="N45" s="9" t="b">
+      <c r="M45" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N45" s="3" t="b">
         <v>0</v>
       </c>
       <c r="O45" s="4" t="s">
@@ -4876,16 +4870,16 @@
       <c r="M50" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="N50" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="O50" s="10" t="s">
+      <c r="N50" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="O50" s="4" t="s">
         <v>338</v>
       </c>
       <c r="P50" s="4" t="s">
         <v>307</v>
       </c>
-      <c r="Q50" s="9" t="b">
+      <c r="Q50" s="3" t="b">
         <v>0</v>
       </c>
       <c r="R50" s="3" t="s">
@@ -4933,16 +4927,16 @@
       <c r="M51" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="N51" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="O51" s="10" t="s">
+      <c r="N51" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="O51" s="4" t="s">
         <v>334</v>
       </c>
       <c r="P51" s="4" t="s">
         <v>289</v>
       </c>
-      <c r="Q51" s="9" t="b">
+      <c r="Q51" s="3" t="b">
         <v>0</v>
       </c>
       <c r="R51" s="3" t="s">

--- a/data/results of data sharing requests.xlsx
+++ b/data/results of data sharing requests.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Ian/git/repository-of-published-irap-data/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C95689FD-6523-E043-83D2-6DD8BEBC831B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E27D0850-080A-EF48-ACED-E4DFDFE1DD97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="32780" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1161,7 +1161,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1311,6 +1311,12 @@
     <font>
       <sz val="12"/>
       <name val="Calibri (Body)"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
@@ -1654,7 +1660,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1677,6 +1683,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -4032,7 +4041,7 @@
       <c r="N35" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="O35" s="7" t="s">
+      <c r="O35" s="9" t="s">
         <v>295</v>
       </c>
       <c r="P35" s="4" t="s">
